--- a/Bases_de_Dados/FootyStats/France Ligue 2_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France Ligue 2_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP223"/>
+  <dimension ref="A1:BP224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>0.42</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.46</v>
@@ -6146,7 +6146,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR26" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.38</v>
@@ -8977,7 +8977,7 @@
         <v>2</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.75</v>
@@ -10070,7 +10070,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR44" t="n">
         <v>1.15</v>
@@ -13558,7 +13558,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR60" t="n">
         <v>0.96</v>
@@ -14209,7 +14209,7 @@
         <v>1.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.08</v>
@@ -17261,7 +17261,7 @@
         <v>1.25</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.92</v>
@@ -18354,7 +18354,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR82" t="n">
         <v>1.11</v>
@@ -21185,7 +21185,7 @@
         <v>0.5</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.5</v>
@@ -22060,7 +22060,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR99" t="n">
         <v>1.04</v>
@@ -25766,7 +25766,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR116" t="n">
         <v>1.6</v>
@@ -25981,7 +25981,7 @@
         <v>1.2</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.27</v>
@@ -27946,7 +27946,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR126" t="n">
         <v>1.8</v>
@@ -28815,7 +28815,7 @@
         <v>1.17</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.5</v>
@@ -31652,7 +31652,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR143" t="n">
         <v>1.45</v>
@@ -32303,7 +32303,7 @@
         <v>1.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.17</v>
@@ -35140,7 +35140,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR159" t="n">
         <v>1.37</v>
@@ -35355,7 +35355,7 @@
         <v>1</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.46</v>
@@ -38407,7 +38407,7 @@
         <v>0.78</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.83</v>
@@ -39500,7 +39500,7 @@
         <v>2</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR179" t="n">
         <v>1.58</v>
@@ -44511,7 +44511,7 @@
         <v>1.18</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.31</v>
@@ -45386,7 +45386,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR206" t="n">
         <v>1.44</v>
@@ -49168,6 +49168,224 @@
       </c>
       <c r="BP223" t="n">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>8207061</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>46081.66666666666</v>
+      </c>
+      <c r="F224" t="n">
+        <v>25</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Pau</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" t="n">
+        <v>1</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
+        <v>3</v>
+      </c>
+      <c r="N224" t="n">
+        <v>3</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>['3', '64', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R224" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S224" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T224" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U224" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V224" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W224" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X224" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU224" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV224" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW224" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB224" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC224" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE224" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BH224" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI224" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ224" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BK224" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL224" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM224" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN224" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO224" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BP224" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/France Ligue 2_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France Ligue 2_20252026.xlsx
@@ -47802,13 +47802,13 @@
         <v>2</v>
       </c>
       <c r="AW217" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX217" t="n">
         <v>7</v>
       </c>
       <c r="AY217" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ217" t="n">
         <v>9</v>
@@ -48677,13 +48677,13 @@
         <v>7</v>
       </c>
       <c r="AX221" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY221" t="n">
         <v>8</v>
       </c>
       <c r="AZ221" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA221" t="n">
         <v>3</v>
@@ -49110,13 +49110,13 @@
         <v>2</v>
       </c>
       <c r="AW223" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX223" t="n">
         <v>8</v>
       </c>
       <c r="AY223" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ223" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/France Ligue 2_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France Ligue 2_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP224"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.38</v>
@@ -2658,7 +2658,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.46</v>
@@ -7018,7 +7018,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR30" t="n">
         <v>1.63</v>
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.67</v>
@@ -12904,7 +12904,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR57" t="n">
         <v>1.74</v>
@@ -13555,7 +13555,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.77</v>
@@ -16610,7 +16610,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR74" t="n">
         <v>1.27</v>
@@ -16825,7 +16825,7 @@
         <v>1</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.31</v>
@@ -21406,7 +21406,7 @@
         <v>2</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR96" t="n">
         <v>1.94</v>
@@ -21621,7 +21621,7 @@
         <v>1.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.46</v>
@@ -25327,7 +25327,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.83</v>
@@ -25984,7 +25984,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR117" t="n">
         <v>1.22</v>
@@ -29036,7 +29036,7 @@
         <v>0.42</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR131" t="n">
         <v>1.45</v>
@@ -29469,7 +29469,7 @@
         <v>1.33</v>
       </c>
       <c r="AP133" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.33</v>
@@ -33832,7 +33832,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR153" t="n">
         <v>1.26</v>
@@ -34701,7 +34701,7 @@
         <v>0.89</v>
       </c>
       <c r="AP157" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ157" t="n">
         <v>1</v>
@@ -38189,7 +38189,7 @@
         <v>1.2</v>
       </c>
       <c r="AP173" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.08</v>
@@ -39282,7 +39282,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR178" t="n">
         <v>1.46</v>
@@ -43206,7 +43206,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR196" t="n">
         <v>1.48</v>
@@ -43639,7 +43639,7 @@
         <v>0.82</v>
       </c>
       <c r="AP198" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ198" t="n">
         <v>0.92</v>
@@ -44293,7 +44293,7 @@
         <v>1.5</v>
       </c>
       <c r="AP201" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ201" t="n">
         <v>1.5</v>
@@ -45604,7 +45604,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR207" t="n">
         <v>1.43</v>
@@ -48235,19 +48235,19 @@
         <v>2</v>
       </c>
       <c r="AV219" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW219" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX219" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY219" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ219" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA219" t="n">
         <v>3</v>
@@ -48459,13 +48459,13 @@
         <v>3</v>
       </c>
       <c r="AX220" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY220" t="n">
         <v>8</v>
       </c>
       <c r="AZ220" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA220" t="n">
         <v>2</v>
@@ -49110,13 +49110,13 @@
         <v>2</v>
       </c>
       <c r="AW223" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX223" t="n">
         <v>8</v>
       </c>
       <c r="AY223" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ223" t="n">
         <v>10</v>
@@ -49386,6 +49386,224 @@
       </c>
       <c r="BP224" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>8206832</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>46083.69791666666</v>
+      </c>
+      <c r="F225" t="n">
+        <v>25</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Amiens SC</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>2</v>
+      </c>
+      <c r="N225" t="n">
+        <v>2</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>['52', '60']</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R225" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S225" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T225" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U225" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V225" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="W225" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X225" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ225" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT225" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU225" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV225" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW225" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX225" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY225" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ225" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA225" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB225" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC225" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BE225" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF225" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG225" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BH225" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI225" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ225" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BK225" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL225" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM225" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN225" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO225" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP225" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/France Ligue 2_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France Ligue 2_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.77</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.31</v>
@@ -3530,7 +3530,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR19" t="n">
         <v>1.16</v>
@@ -4838,7 +4838,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR20" t="n">
         <v>0.57</v>
@@ -5053,7 +5053,7 @@
         <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.08</v>
@@ -5271,10 +5271,10 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR22" t="n">
         <v>1.15</v>
@@ -5707,10 +5707,10 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR24" t="n">
         <v>2.34</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.77</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.38</v>
@@ -6579,10 +6579,10 @@
         <v>1</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR28" t="n">
         <v>1.12</v>
@@ -6800,7 +6800,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR29" t="n">
         <v>2.82</v>
@@ -7236,7 +7236,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR31" t="n">
         <v>0.74</v>
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.58</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.31</v>
@@ -8108,7 +8108,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR35" t="n">
         <v>1.54</v>
@@ -8326,7 +8326,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR36" t="n">
         <v>1.9</v>
@@ -8541,7 +8541,7 @@
         <v>2</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ37" t="n">
         <v>1</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.46</v>
@@ -8977,7 +8977,7 @@
         <v>2</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.75</v>
@@ -9198,7 +9198,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR40" t="n">
         <v>1.17</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.08</v>
@@ -10288,7 +10288,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR45" t="n">
         <v>1.65</v>
@@ -10503,10 +10503,10 @@
         <v>0.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR46" t="n">
         <v>1.02</v>
@@ -10721,10 +10721,10 @@
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR47" t="n">
         <v>1.75</v>
@@ -11157,10 +11157,10 @@
         <v>2</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR49" t="n">
         <v>1.29</v>
@@ -11378,7 +11378,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR50" t="n">
         <v>1.18</v>
@@ -11593,7 +11593,7 @@
         <v>2.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.75</v>
@@ -11811,7 +11811,7 @@
         <v>1</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.58</v>
@@ -12029,10 +12029,10 @@
         <v>1.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR53" t="n">
         <v>2.11</v>
@@ -12250,7 +12250,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR54" t="n">
         <v>1.33</v>
@@ -13773,10 +13773,10 @@
         <v>0.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR61" t="n">
         <v>1.42</v>
@@ -14209,7 +14209,7 @@
         <v>1.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.08</v>
@@ -14430,7 +14430,7 @@
         <v>2</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR64" t="n">
         <v>1.61</v>
@@ -14645,7 +14645,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.58</v>
@@ -14866,7 +14866,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR66" t="n">
         <v>1.03</v>
@@ -15081,7 +15081,7 @@
         <v>0.5</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.38</v>
@@ -15299,10 +15299,10 @@
         <v>1.5</v>
       </c>
       <c r="AP68" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR68" t="n">
         <v>2.18</v>
@@ -15738,7 +15738,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR70" t="n">
         <v>1.44</v>
@@ -15953,10 +15953,10 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR71" t="n">
         <v>1.39</v>
@@ -16174,7 +16174,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR72" t="n">
         <v>2</v>
@@ -16389,7 +16389,7 @@
         <v>2.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.75</v>
@@ -16607,7 +16607,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.42</v>
@@ -17261,10 +17261,10 @@
         <v>1.25</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR77" t="n">
         <v>1.3</v>
@@ -17918,7 +17918,7 @@
         <v>2</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR80" t="n">
         <v>1.78</v>
@@ -18569,7 +18569,7 @@
         <v>1</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.38</v>
@@ -18787,10 +18787,10 @@
         <v>0.4</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR84" t="n">
         <v>1.94</v>
@@ -19005,10 +19005,10 @@
         <v>1.5</v>
       </c>
       <c r="AP85" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR85" t="n">
         <v>1.09</v>
@@ -19444,7 +19444,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR87" t="n">
         <v>1.08</v>
@@ -19662,7 +19662,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR88" t="n">
         <v>1.6</v>
@@ -19877,7 +19877,7 @@
         <v>2.6</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.75</v>
@@ -20313,10 +20313,10 @@
         <v>1.75</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR91" t="n">
         <v>1.27</v>
@@ -20531,7 +20531,7 @@
         <v>1.5</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.31</v>
@@ -20752,7 +20752,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR93" t="n">
         <v>1.44</v>
@@ -20970,7 +20970,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR94" t="n">
         <v>1.62</v>
@@ -21185,7 +21185,7 @@
         <v>0.5</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.5</v>
@@ -22278,7 +22278,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR100" t="n">
         <v>1.1</v>
@@ -22496,7 +22496,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR101" t="n">
         <v>1.16</v>
@@ -22711,10 +22711,10 @@
         <v>1.5</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR102" t="n">
         <v>1.61</v>
@@ -22929,10 +22929,10 @@
         <v>0.33</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR103" t="n">
         <v>1.44</v>
@@ -23365,7 +23365,7 @@
         <v>1</v>
       </c>
       <c r="AP105" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.38</v>
@@ -23801,7 +23801,7 @@
         <v>1.2</v>
       </c>
       <c r="AP107" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.5</v>
@@ -24019,10 +24019,10 @@
         <v>2</v>
       </c>
       <c r="AP108" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR108" t="n">
         <v>1.81</v>
@@ -24458,7 +24458,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR110" t="n">
         <v>1.56</v>
@@ -25109,7 +25109,7 @@
         <v>1.33</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ113" t="n">
         <v>1</v>
@@ -25330,7 +25330,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR114" t="n">
         <v>0.93</v>
@@ -25981,7 +25981,7 @@
         <v>1.2</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.42</v>
@@ -26417,7 +26417,7 @@
         <v>1</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.08</v>
@@ -26638,7 +26638,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR120" t="n">
         <v>1.56</v>
@@ -27074,7 +27074,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR122" t="n">
         <v>1.17</v>
@@ -27725,7 +27725,7 @@
         <v>2.29</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.75</v>
@@ -27943,7 +27943,7 @@
         <v>1.86</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.77</v>
@@ -28164,7 +28164,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR127" t="n">
         <v>1.17</v>
@@ -28379,10 +28379,10 @@
         <v>1</v>
       </c>
       <c r="AP128" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR128" t="n">
         <v>1.09</v>
@@ -28597,7 +28597,7 @@
         <v>1.33</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.5</v>
@@ -28815,7 +28815,7 @@
         <v>1.17</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.5</v>
@@ -29033,7 +29033,7 @@
         <v>1.17</v>
       </c>
       <c r="AP131" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.42</v>
@@ -29254,7 +29254,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR132" t="n">
         <v>1.5</v>
@@ -29472,7 +29472,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR133" t="n">
         <v>1.05</v>
@@ -29908,7 +29908,7 @@
         <v>2</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR135" t="n">
         <v>1.72</v>
@@ -30341,10 +30341,10 @@
         <v>1.43</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR137" t="n">
         <v>1.35</v>
@@ -30780,7 +30780,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR139" t="n">
         <v>1.44</v>
@@ -31431,7 +31431,7 @@
         <v>1</v>
       </c>
       <c r="AP142" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.46</v>
@@ -32303,10 +32303,10 @@
         <v>1.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR146" t="n">
         <v>1.34</v>
@@ -32521,7 +32521,7 @@
         <v>1.29</v>
       </c>
       <c r="AP147" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.5</v>
@@ -32739,10 +32739,10 @@
         <v>1.57</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR148" t="n">
         <v>1.46</v>
@@ -32957,10 +32957,10 @@
         <v>1.13</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR149" t="n">
         <v>1.41</v>
@@ -33178,7 +33178,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR150" t="n">
         <v>1.21</v>
@@ -33614,7 +33614,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR152" t="n">
         <v>1.64</v>
@@ -33829,7 +33829,7 @@
         <v>1.43</v>
       </c>
       <c r="AP153" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.42</v>
@@ -34047,7 +34047,7 @@
         <v>2.13</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.75</v>
@@ -34486,7 +34486,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR156" t="n">
         <v>1.45</v>
@@ -34922,7 +34922,7 @@
         <v>2</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR158" t="n">
         <v>1.66</v>
@@ -35137,7 +35137,7 @@
         <v>1.78</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ159" t="n">
         <v>1.77</v>
@@ -35355,7 +35355,7 @@
         <v>1</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.46</v>
@@ -36009,7 +36009,7 @@
         <v>1.63</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.5</v>
@@ -36227,10 +36227,10 @@
         <v>1.38</v>
       </c>
       <c r="AP164" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR164" t="n">
         <v>1.22</v>
@@ -36448,7 +36448,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR165" t="n">
         <v>1.28</v>
@@ -36881,10 +36881,10 @@
         <v>0.33</v>
       </c>
       <c r="AP167" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR167" t="n">
         <v>1.38</v>
@@ -37099,7 +37099,7 @@
         <v>1.44</v>
       </c>
       <c r="AP168" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.38</v>
@@ -37538,7 +37538,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR170" t="n">
         <v>1.7</v>
@@ -37753,10 +37753,10 @@
         <v>1.38</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR171" t="n">
         <v>1.48</v>
@@ -37974,7 +37974,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR172" t="n">
         <v>1.41</v>
@@ -38407,10 +38407,10 @@
         <v>0.78</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR174" t="n">
         <v>1.52</v>
@@ -38625,7 +38625,7 @@
         <v>1</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ175" t="n">
         <v>1.46</v>
@@ -38846,7 +38846,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR176" t="n">
         <v>1.26</v>
@@ -39715,7 +39715,7 @@
         <v>1.67</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.5</v>
@@ -39936,7 +39936,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR181" t="n">
         <v>1.21</v>
@@ -40154,7 +40154,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR182" t="n">
         <v>1.49</v>
@@ -40369,7 +40369,7 @@
         <v>2</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.75</v>
@@ -40805,7 +40805,7 @@
         <v>1.44</v>
       </c>
       <c r="AP185" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ185" t="n">
         <v>1.58</v>
@@ -41244,7 +41244,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR187" t="n">
         <v>1.32</v>
@@ -41459,7 +41459,7 @@
         <v>1.56</v>
       </c>
       <c r="AP188" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.5</v>
@@ -42116,7 +42116,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR191" t="n">
         <v>1.28</v>
@@ -42331,7 +42331,7 @@
         <v>1.2</v>
       </c>
       <c r="AP192" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.46</v>
@@ -42552,7 +42552,7 @@
         <v>2</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR193" t="n">
         <v>1.54</v>
@@ -42770,7 +42770,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR194" t="n">
         <v>1.28</v>
@@ -42985,7 +42985,7 @@
         <v>1.18</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ195" t="n">
         <v>1.08</v>
@@ -43203,7 +43203,7 @@
         <v>1.44</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ196" t="n">
         <v>1.42</v>
@@ -43424,7 +43424,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR197" t="n">
         <v>1.59</v>
@@ -43642,7 +43642,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ198" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR198" t="n">
         <v>1.13</v>
@@ -44075,10 +44075,10 @@
         <v>1.36</v>
       </c>
       <c r="AP200" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR200" t="n">
         <v>1.27</v>
@@ -44511,7 +44511,7 @@
         <v>1.18</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.31</v>
@@ -45819,10 +45819,10 @@
         <v>0.75</v>
       </c>
       <c r="AP208" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR208" t="n">
         <v>1.2</v>
@@ -46255,10 +46255,10 @@
         <v>1.27</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ210" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR210" t="n">
         <v>1.38</v>
@@ -46476,7 +46476,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ211" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR211" t="n">
         <v>1.3</v>
@@ -46691,10 +46691,10 @@
         <v>0.82</v>
       </c>
       <c r="AP212" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ212" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR212" t="n">
         <v>1.45</v>
@@ -46912,7 +46912,7 @@
         <v>2</v>
       </c>
       <c r="AQ213" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR213" t="n">
         <v>1.53</v>
@@ -47127,7 +47127,7 @@
         <v>1.73</v>
       </c>
       <c r="AP214" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ214" t="n">
         <v>1.58</v>
@@ -47563,10 +47563,10 @@
         <v>1.36</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR216" t="n">
         <v>1.35</v>
@@ -48435,7 +48435,7 @@
         <v>1</v>
       </c>
       <c r="AP220" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AQ220" t="n">
         <v>1</v>
@@ -48656,7 +48656,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR221" t="n">
         <v>1.46</v>
@@ -49307,7 +49307,7 @@
         <v>1.67</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ224" t="n">
         <v>1.77</v>
@@ -49604,6 +49604,1532 @@
       </c>
       <c r="BP225" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>8207005</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F226" t="n">
+        <v>26</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Pau</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>2</v>
+      </c>
+      <c r="J226" t="n">
+        <v>1</v>
+      </c>
+      <c r="K226" t="n">
+        <v>3</v>
+      </c>
+      <c r="L226" t="n">
+        <v>2</v>
+      </c>
+      <c r="M226" t="n">
+        <v>2</v>
+      </c>
+      <c r="N226" t="n">
+        <v>4</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>['4', '31']</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>['13', '90+3']</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R226" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S226" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T226" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U226" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V226" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W226" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X226" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN226" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV226" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW226" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX226" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY226" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA226" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB226" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC226" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE226" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF226" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG226" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BH226" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BI226" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BJ226" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BK226" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BL226" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BM226" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BN226" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BO226" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP226" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>8206992</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F227" t="n">
+        <v>26</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>1</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>1</v>
+      </c>
+      <c r="L227" t="n">
+        <v>2</v>
+      </c>
+      <c r="M227" t="n">
+        <v>2</v>
+      </c>
+      <c r="N227" t="n">
+        <v>4</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>['36', '83']</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>['53', '69']</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R227" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S227" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T227" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U227" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V227" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W227" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X227" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AQ227" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT227" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AU227" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV227" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW227" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX227" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY227" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ227" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA227" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB227" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC227" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BE227" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF227" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BG227" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH227" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BI227" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BJ227" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BK227" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BL227" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BM227" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BN227" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO227" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP227" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>8206924</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F228" t="n">
+        <v>26</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Grenoble Foot 38</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>1</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>1</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R228" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S228" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T228" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U228" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V228" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W228" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X228" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU228" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW228" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY228" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA228" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB228" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC228" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE228" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF228" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG228" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH228" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI228" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ228" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK228" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL228" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM228" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN228" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO228" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP228" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>8206953</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F229" t="n">
+        <v>26</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>1</v>
+      </c>
+      <c r="K229" t="n">
+        <v>1</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" t="n">
+        <v>3</v>
+      </c>
+      <c r="N229" t="n">
+        <v>3</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>['9', '76', '81']</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R229" t="n">
+        <v>2</v>
+      </c>
+      <c r="S229" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T229" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U229" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V229" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W229" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X229" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV229" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA229" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB229" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC229" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BE229" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF229" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG229" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH229" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI229" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BJ229" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK229" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL229" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BM229" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN229" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO229" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP229" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>8207104</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F230" t="n">
+        <v>26</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Boulogne</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Amiens SC</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>1</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" t="n">
+        <v>2</v>
+      </c>
+      <c r="L230" t="n">
+        <v>4</v>
+      </c>
+      <c r="M230" t="n">
+        <v>2</v>
+      </c>
+      <c r="N230" t="n">
+        <v>6</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>['42', '58', '77', '90+6']</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>['10', '73']</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R230" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S230" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T230" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U230" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V230" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W230" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X230" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AU230" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY230" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA230" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB230" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC230" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BE230" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF230" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BG230" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH230" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI230" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BJ230" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BK230" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL230" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BM230" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN230" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BO230" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP230" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>8206914</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>46088.41666666666</v>
+      </c>
+      <c r="F231" t="n">
+        <v>26</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" t="n">
+        <v>2</v>
+      </c>
+      <c r="M231" t="n">
+        <v>1</v>
+      </c>
+      <c r="N231" t="n">
+        <v>3</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>['78', '81']</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R231" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S231" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="T231" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U231" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V231" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W231" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X231" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM231" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN231" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AQ231" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AR231" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS231" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT231" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU231" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW231" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY231" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA231" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB231" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC231" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD231" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BE231" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF231" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG231" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH231" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI231" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ231" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK231" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BL231" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM231" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BN231" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO231" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP231" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="n">
+        <v>8207062</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>46088.41666666666</v>
+      </c>
+      <c r="F232" t="n">
+        <v>26</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Le Mans</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>2</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>2</v>
+      </c>
+      <c r="L232" t="n">
+        <v>3</v>
+      </c>
+      <c r="M232" t="n">
+        <v>0</v>
+      </c>
+      <c r="N232" t="n">
+        <v>3</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>['16', '18', '65']</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R232" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S232" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="T232" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U232" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V232" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W232" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X232" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK232" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM232" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN232" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO232" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP232" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ232" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR232" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS232" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT232" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU232" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV232" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW232" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX232" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY232" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ232" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA232" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB232" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC232" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD232" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE232" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF232" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BG232" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH232" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BI232" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BJ232" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK232" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BL232" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM232" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN232" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO232" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP232" t="n">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/France Ligue 2_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France Ligue 2_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP232"/>
+  <dimension ref="A1:BP233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.46</v>
@@ -5928,7 +5928,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR25" t="n">
         <v>1.65</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.77</v>
@@ -8980,7 +8980,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR39" t="n">
         <v>1.06</v>
@@ -11596,7 +11596,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR51" t="n">
         <v>1.4</v>
@@ -12465,7 +12465,7 @@
         <v>0.67</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.38</v>
@@ -16171,7 +16171,7 @@
         <v>1</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.31</v>
@@ -16392,7 +16392,7 @@
         <v>1</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR73" t="n">
         <v>0.9399999999999999</v>
@@ -19880,7 +19880,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR89" t="n">
         <v>1.54</v>
@@ -20095,7 +20095,7 @@
         <v>0.75</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.5</v>
@@ -23147,7 +23147,7 @@
         <v>1.8</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.58</v>
@@ -23586,7 +23586,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR106" t="n">
         <v>1.52</v>
@@ -27728,7 +27728,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR125" t="n">
         <v>1.37</v>
@@ -29687,7 +29687,7 @@
         <v>1.14</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ134" t="n">
         <v>1</v>
@@ -33611,7 +33611,7 @@
         <v>0.25</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.6899999999999999</v>
@@ -34050,7 +34050,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR154" t="n">
         <v>1.9</v>
@@ -37320,7 +37320,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR169" t="n">
         <v>1.25</v>
@@ -37535,7 +37535,7 @@
         <v>1</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.86</v>
@@ -40372,7 +40372,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR183" t="n">
         <v>1.41</v>
@@ -41677,7 +41677,7 @@
         <v>1</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.31</v>
@@ -43421,7 +43421,7 @@
         <v>1.4</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ197" t="n">
         <v>1.31</v>
@@ -46040,7 +46040,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR209" t="n">
         <v>1.31</v>
@@ -47345,7 +47345,7 @@
         <v>1.17</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.08</v>
@@ -50854,16 +50854,16 @@
         <v>2</v>
       </c>
       <c r="AW231" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY231" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ231" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA231" t="n">
         <v>6</v>
@@ -51075,13 +51075,13 @@
         <v>9</v>
       </c>
       <c r="AX232" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY232" t="n">
         <v>15</v>
       </c>
       <c r="AZ232" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA232" t="n">
         <v>6</v>
@@ -51130,6 +51130,224 @@
       </c>
       <c r="BP232" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="n">
+        <v>8206954</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>46088.66666666666</v>
+      </c>
+      <c r="F233" t="n">
+        <v>26</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>2</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0</v>
+      </c>
+      <c r="N233" t="n">
+        <v>2</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>['65', '80']</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R233" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S233" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="T233" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U233" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V233" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W233" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X233" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AN233" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO233" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ233" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS233" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT233" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU233" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW233" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX233" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY233" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ233" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA233" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB233" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC233" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD233" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE233" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF233" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG233" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH233" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BI233" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BJ233" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BK233" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BL233" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BM233" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BN233" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BO233" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BP233" t="n">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/France Ligue 2_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France Ligue 2_20252026.xlsx
@@ -49979,7 +49979,7 @@
         <v>11</v>
       </c>
       <c r="AV227" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW227" t="n">
         <v>8</v>
@@ -49991,7 +49991,7 @@
         <v>19</v>
       </c>
       <c r="AZ227" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA227" t="n">
         <v>6</v>
@@ -50194,22 +50194,22 @@
         <v>2.68</v>
       </c>
       <c r="AU228" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV228" t="n">
         <v>2</v>
       </c>
       <c r="AW228" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY228" t="n">
         <v>12</v>
       </c>
       <c r="AZ228" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA228" t="n">
         <v>7</v>
@@ -50418,13 +50418,13 @@
         <v>4</v>
       </c>
       <c r="AW229" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX229" t="n">
         <v>4</v>
       </c>
       <c r="AY229" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ229" t="n">
         <v>8</v>
@@ -50854,13 +50854,13 @@
         <v>2</v>
       </c>
       <c r="AW231" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX231" t="n">
         <v>2</v>
       </c>
       <c r="AY231" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ231" t="n">
         <v>4</v>
@@ -51072,13 +51072,13 @@
         <v>3</v>
       </c>
       <c r="AW232" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX232" t="n">
         <v>7</v>
       </c>
       <c r="AY232" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ232" t="n">
         <v>10</v>
